--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_47.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4292602.704160013</v>
+        <v>4328920.152355722</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117094477</v>
+        <v>987.0883260128384</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117094477</v>
+        <v>987.0883260128384</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20558356.68881374</v>
+        <v>20557546.73593489</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>80.07191941636528</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274.1753087095286</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>374</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>146.6703221531804</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>117.4799874759381</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>374</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>374</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>285.1318526462773</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1219,16 +1219,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>288.7997011341715</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>106.0748691037268</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.83504507946625</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H12" t="n">
-        <v>177.6137898608468</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,19 +1489,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1553,25 +1553,25 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O13" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S13" t="n">
         <v>30.56285675203577</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
@@ -1690,16 +1690,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>177.613789860847</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,25 +1732,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>284.9649587918013</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1790,28 +1790,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O16" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090244067</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1921,16 +1921,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1984,10 +1984,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273604</v>
       </c>
       <c r="Y18" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2042,13 +2042,13 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q19" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R19" t="n">
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090244146</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160.9993129555745</v>
+        <v>161.4599003208889</v>
       </c>
       <c r="C20" t="n">
         <v>128.4745782429939</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T20" t="n">
         <v>259.6218731858503</v>
@@ -2328,7 +2328,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
         <v>72.84688483418068</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2373,7 +2373,7 @@
         <v>328.1106633827815</v>
       </c>
       <c r="V23" t="n">
-        <v>308.8510241668239</v>
+        <v>309.311611532138</v>
       </c>
       <c r="W23" t="n">
         <v>317.3734759809475</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2443,22 +2443,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090244506</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653141466</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038859</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,19 +2677,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V27" t="n">
-        <v>267.1024830734935</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
@@ -2750,13 +2750,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2802,13 +2802,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2872,19 +2872,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,22 +2911,22 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
-        <v>188.4739349641461</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>111.3731429098285</v>
@@ -2935,7 +2935,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481075</v>
       </c>
     </row>
     <row r="31">
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>83.88962870801186</v>
+        <v>84.350216073326</v>
       </c>
       <c r="G32" t="n">
         <v>81.37445771415189</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3106,16 +3106,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>192.2280582198497</v>
       </c>
       <c r="G33" t="n">
         <v>3.999611346725456</v>
@@ -3148,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
@@ -3163,10 +3163,10 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3279,7 +3279,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3343,10 +3343,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -3406,7 +3406,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273604</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>113.5995101105027</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H39" t="n">
         <v>4.021973978873961</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
         <v>180.333570877285</v>
@@ -3631,7 +3631,7 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T39" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U39" t="n">
         <v>79.16168051490372</v>
@@ -3695,7 +3695,7 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O40" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
         <v>291.4220612627037</v>
@@ -3707,7 +3707,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
         <v>72.84688483418068</v>
@@ -3817,7 +3817,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -3826,16 +3826,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>173.5918158819734</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>353.9253867592579</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3880,7 +3880,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -4054,16 +4054,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>3.999611346725456</v>
@@ -4072,7 +4072,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>173.5918158819732</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
@@ -4108,7 +4108,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
         <v>414.5106671915202</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>56.81417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>46.37058683203599</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>41.96322359277473</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.02420469579306</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>319.5000270351759</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>384.1900000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>753.46</v>
       </c>
       <c r="N2" t="n">
-        <v>886.1402453266331</v>
+        <v>1122.73</v>
       </c>
       <c r="O2" t="n">
-        <v>1256.400245326633</v>
+        <v>1122.73</v>
       </c>
       <c r="P2" t="n">
-        <v>1314.492137192891</v>
+        <v>1492</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.183143567852</v>
+        <v>1491.999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1405.724707412505</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1218.99441573196</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>967.2891925799699</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>735.1164408963094</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>494.3351520266654</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>300.1110778239707</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>187.6692266292168</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.6095073802453</v>
+        <v>701.7129606495888</v>
       </c>
       <c r="C3" t="n">
-        <v>241.6095073802453</v>
+        <v>701.7129606495888</v>
       </c>
       <c r="D3" t="n">
-        <v>241.6095073802453</v>
+        <v>701.7129606495888</v>
       </c>
       <c r="E3" t="n">
-        <v>241.6095073802453</v>
+        <v>701.7129606495888</v>
       </c>
       <c r="F3" t="n">
-        <v>241.6095073802453</v>
+        <v>358.6460491971879</v>
       </c>
       <c r="G3" t="n">
-        <v>241.6095073802453</v>
+        <v>29.84</v>
       </c>
       <c r="H3" t="n">
-        <v>241.6095073802453</v>
+        <v>29.84</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>398.6635894772295</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>717.174568996958</v>
+        <v>718.1019687139392</v>
       </c>
       <c r="M3" t="n">
-        <v>858.2892107398172</v>
+        <v>859.7561604567984</v>
       </c>
       <c r="N3" t="n">
-        <v>1048.06018421531</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1338.780579861293</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.786030368536</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1346.247111942856</v>
+        <v>1492</v>
       </c>
       <c r="R3" t="n">
-        <v>968.469334165078</v>
+        <v>1357.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>590.6915563873001</v>
+        <v>1294.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>586.1729256167982</v>
+        <v>917.2855583262723</v>
       </c>
       <c r="U3" t="n">
-        <v>585.9750207704118</v>
+        <v>769.1337177675042</v>
       </c>
       <c r="V3" t="n">
-        <v>571.3177811830177</v>
+        <v>754.4764781801101</v>
       </c>
       <c r="W3" t="n">
-        <v>538.6176368296556</v>
+        <v>721.776333826748</v>
       </c>
       <c r="X3" t="n">
-        <v>518.5542636524964</v>
+        <v>701.7129606495888</v>
       </c>
       <c r="Y3" t="n">
-        <v>518.5542636524964</v>
+        <v>701.7129606495888</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>704.5799155149155</v>
+        <v>1250.627100357226</v>
       </c>
       <c r="C4" t="n">
-        <v>704.5799155149155</v>
+        <v>1376.629106175661</v>
       </c>
       <c r="D4" t="n">
-        <v>704.5799155149155</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="E4" t="n">
-        <v>704.5799155149155</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="F4" t="n">
-        <v>704.5799155149155</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="G4" t="n">
-        <v>704.5799155149155</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="H4" t="n">
-        <v>704.5799155149155</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>259.1561373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>505.7585226289696</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="V4" t="n">
-        <v>704.5799155149155</v>
+        <v>704.5387527280302</v>
       </c>
       <c r="W4" t="n">
-        <v>704.5799155149155</v>
+        <v>876.4296709877076</v>
       </c>
       <c r="X4" t="n">
-        <v>704.5799155149155</v>
+        <v>1027.460462011901</v>
       </c>
       <c r="Y4" t="n">
-        <v>704.5799155149155</v>
+        <v>1138.869762690933</v>
       </c>
     </row>
     <row r="5">
@@ -4534,46 +4534,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>697.388108133742</v>
+        <v>464.9696632645968</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
         <v>1125.74</v>
@@ -4582,28 +4582,28 @@
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1496</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>724.4391204399794</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="C6" t="n">
-        <v>724.4391204399794</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1115.008252590758</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S6" t="n">
-        <v>1051.888241191398</v>
+        <v>593.9829508193566</v>
       </c>
       <c r="T6" t="n">
-        <v>1047.369610420896</v>
+        <v>216.2051730415787</v>
       </c>
       <c r="U6" t="n">
-        <v>1047.17170557451</v>
+        <v>216.0074111340145</v>
       </c>
       <c r="V6" t="n">
-        <v>1032.514465987116</v>
+        <v>201.3501715466204</v>
       </c>
       <c r="W6" t="n">
-        <v>744.5024936171386</v>
+        <v>168.6500271932582</v>
       </c>
       <c r="X6" t="n">
-        <v>724.4391204399794</v>
+        <v>148.5866540160991</v>
       </c>
       <c r="Y6" t="n">
-        <v>724.4391204399794</v>
+        <v>148.5866540160991</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>774.8297405151413</v>
+        <v>1021.390962989494</v>
       </c>
       <c r="C7" t="n">
-        <v>900.8317463335771</v>
+        <v>1147.392968807929</v>
       </c>
       <c r="D7" t="n">
-        <v>1014.150890458577</v>
+        <v>1260.712112932929</v>
       </c>
       <c r="E7" t="n">
-        <v>1016.483548464727</v>
+        <v>1378.541017144342</v>
       </c>
       <c r="F7" t="n">
-        <v>1016.483548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G7" t="n">
-        <v>1016.483548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H7" t="n">
-        <v>1016.483548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>1016.483548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
@@ -4749,19 +4749,19 @@
         <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>276.4812224743522</v>
       </c>
       <c r="V7" t="n">
-        <v>228.741392885946</v>
+        <v>475.3026153602981</v>
       </c>
       <c r="W7" t="n">
-        <v>400.6323111456234</v>
+        <v>647.1935336199756</v>
       </c>
       <c r="X7" t="n">
-        <v>551.6631021698169</v>
+        <v>798.2243246441691</v>
       </c>
       <c r="Y7" t="n">
-        <v>663.0724028488492</v>
+        <v>909.6336253232014</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4798,49 +4798,49 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>451.8183303517587</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M8" t="n">
-        <v>886.1402453266331</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="N8" t="n">
-        <v>1256.400245326633</v>
+        <v>1205.389972964824</v>
       </c>
       <c r="O8" t="n">
-        <v>1256.400245326633</v>
+        <v>1205.389972964824</v>
       </c>
       <c r="P8" t="n">
-        <v>1314.492137192891</v>
+        <v>1264.054179353695</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>740.8008178458908</v>
       </c>
       <c r="C9" t="n">
-        <v>1222.526720202428</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="D9" t="n">
-        <v>1222.526720202428</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>876.3932886651428</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>533.3263772127418</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1388.653752940529</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1253.786643039707</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1190.706988034478</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1186.197114649148</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1185.999352741584</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>1171.34211315419</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>1138.641968800828</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1118.578595623669</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>1118.578595623669</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>832.2162197871305</v>
+        <v>481.5694783410938</v>
       </c>
       <c r="C10" t="n">
-        <v>958.2182256055663</v>
+        <v>607.5714841595295</v>
       </c>
       <c r="D10" t="n">
-        <v>1071.537369730566</v>
+        <v>720.8906282845296</v>
       </c>
       <c r="E10" t="n">
-        <v>1189.366273941979</v>
+        <v>838.7195324959426</v>
       </c>
       <c r="F10" t="n">
-        <v>1313.727246533915</v>
+        <v>963.0805050878781</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>963.0805050878781</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="V10" t="n">
-        <v>458.0187904176125</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="W10" t="n">
-        <v>458.0187904176125</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="X10" t="n">
-        <v>609.049581441806</v>
+        <v>369.8121406748016</v>
       </c>
       <c r="Y10" t="n">
-        <v>720.4588821208383</v>
+        <v>369.8121406748016</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D11" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G11" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>1418.446838088717</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M11" t="n">
-        <v>1595.767892278425</v>
+        <v>2060.500475851726</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5068,16 +5068,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W11" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>992.2829698086705</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C12" t="n">
-        <v>951.7780077424894</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D12" t="n">
-        <v>600.3257987549109</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E12" t="n">
-        <v>254.1923672176254</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>235.3678800076488</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G12" t="n">
-        <v>231.32786854631</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X12" t="n">
-        <v>1459.907161134389</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y12" t="n">
-        <v>1380.723936118091</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="13">
@@ -5202,7 +5202,7 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
         <v>1115.142339091088</v>
@@ -5211,7 +5211,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R13" t="n">
         <v>82.79157247680381</v>
@@ -5245,49 +5245,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C14" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D14" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E14" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G14" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>310.7478922784252</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>953.2578922784252</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>1595.767892278425</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M14" t="n">
-        <v>2238.277892278425</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5305,16 +5305,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W14" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>343.7981213238222</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C15" t="n">
-        <v>303.293159257641</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D15" t="n">
-        <v>276.0833745124868</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>254.1923672176256</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>235.367880007649</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>911.2836656246793</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X15" t="n">
-        <v>487.1798884071161</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y15" t="n">
-        <v>407.9966633908188</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="16">
@@ -5415,43 +5415,43 @@
         <v>809.1641510572457</v>
       </c>
       <c r="F16" t="n">
-        <v>855.3151236491833</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G16" t="n">
-        <v>931.1258141262325</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H16" t="n">
-        <v>1027.892525187269</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I16" t="n">
-        <v>1189.283805434828</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J16" t="n">
-        <v>1515.576154611869</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K16" t="n">
-        <v>1619.080700024148</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1608.654647405758</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1505.227982468591</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605488</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
-        <v>1114.295626111699</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645235</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881619</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741483</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,49 +5509,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M17" t="n">
-        <v>1592.599638490728</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N17" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O17" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P17" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1316.525394051095</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C18" t="n">
-        <v>1100.675163417264</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D18" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5627,10 +5627,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X18" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y18" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="19">
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6440969023998</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4361027208356</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5452468458357</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E19" t="n">
-        <v>809.1641510572487</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F19" t="n">
-        <v>855.3151236491841</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G19" t="n">
-        <v>931.1258141262333</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H19" t="n">
-        <v>1027.89252518727</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I19" t="n">
-        <v>1189.283805434829</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J19" t="n">
-        <v>1515.57615461187</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K19" t="n">
-        <v>1619.080700024148</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405759</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468592</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605489</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.2956261117</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645243</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881626</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741562</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5709,7 +5709,7 @@
         <v>619.8974585570725</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.0967592361077</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M20" t="n">
-        <v>1009.32297330616</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N20" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O20" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5770,25 +5770,25 @@
         <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="21">
@@ -5968,7 +5968,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G23" t="n">
         <v>125.5027119537179</v>
@@ -5980,40 +5980,40 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>737.2059437357115</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L23" t="n">
-        <v>953.2578922784251</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1595.767892278425</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N23" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O23" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
         <v>1546.122070632377</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6089,22 +6089,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>311.8346198394665</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.6440969024035</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4361027208392</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5452468458393</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E25" t="n">
-        <v>809.1641510572523</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F25" t="n">
-        <v>855.3151236491877</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1258141262369</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.892525187274</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.283805434832</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J25" t="n">
-        <v>1515.576154611874</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K25" t="n">
-        <v>1619.080700024152</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405763</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468595</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605493</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111704</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645279</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881663</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741926</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6183,7 +6183,7 @@
         <v>619.8974585570725</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.0967592361113</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="26">
@@ -6193,46 +6193,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H26" t="n">
-        <v>52.38523976294358</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L26" t="n">
-        <v>1376.091327711023</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M26" t="n">
-        <v>1792.359898617045</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>1792.359898617045</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
         <v>2596</v>
@@ -6253,16 +6253,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W26" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>816.937701241021</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C27" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000655</v>
       </c>
       <c r="D27" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124871</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F27" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6320,28 +6320,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V27" t="n">
-        <v>1496.92136969322</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.423245541878</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X27" t="n">
-        <v>1284.561892566739</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y27" t="n">
-        <v>1205.378667550442</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="28">
@@ -6396,7 +6396,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D29" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G29" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H29" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
@@ -6457,13 +6457,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M29" t="n">
-        <v>2060.956838088718</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N29" t="n">
         <v>2238.277892278425</v>
@@ -6478,28 +6478,28 @@
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S29" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W29" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="30">
@@ -6515,16 +6515,16 @@
         <v>776.43273917484</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,28 +6554,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>1284.561892566739</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
         <v>1205.378667550442</v>
@@ -6621,22 +6621,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N31" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R31" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
         <v>207.6991338872046</v>
@@ -6697,10 +6697,10 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L32" t="n">
-        <v>1009.32297330616</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M32" t="n">
-        <v>1651.83297330616</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N32" t="n">
         <v>1651.83297330616</v>
@@ -6715,28 +6715,28 @@
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1237.102618183067</v>
+        <v>343.7981213238219</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>303.2931592576408</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>276.0833745124866</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176254</v>
       </c>
       <c r="F33" t="n">
         <v>60.02261143999941</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S33" t="n">
-        <v>1849.457698584356</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T33" t="n">
-        <v>1767.260375227614</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U33" t="n">
-        <v>1687.299081778216</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V33" t="n">
-        <v>1592.843862392842</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W33" t="n">
-        <v>1480.3457382415</v>
+        <v>587.0412413822548</v>
       </c>
       <c r="X33" t="n">
-        <v>1380.484385266361</v>
+        <v>487.1798884071159</v>
       </c>
       <c r="Y33" t="n">
-        <v>1301.301160250064</v>
+        <v>407.9966633908185</v>
       </c>
     </row>
     <row r="34">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C35" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D35" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E35" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G35" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H35" t="n">
         <v>51.92</v>
@@ -6928,52 +6928,52 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N35" t="n">
-        <v>2234.653276253736</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O35" t="n">
-        <v>2395.783377636692</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P35" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S35" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W35" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="36">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1316.525394051095</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C36" t="n">
-        <v>1100.675163417264</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D36" t="n">
         <v>749.2229544296858</v>
@@ -7049,10 +7049,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y36" t="n">
-        <v>1380.723936118091</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="37">
@@ -7165,25 +7165,25 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M38" t="n">
-        <v>1009.32297330616</v>
+        <v>2060.500475851726</v>
       </c>
       <c r="N38" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O38" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P38" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1141.180125483445</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C39" t="n">
-        <v>776.43273917484</v>
+        <v>872.355231874462</v>
       </c>
       <c r="D39" t="n">
-        <v>424.9805301872616</v>
+        <v>845.1454471293079</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>499.0120155920224</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G39" t="n">
         <v>55.98259997866057</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R39" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S39" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X39" t="n">
-        <v>1459.907161134389</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y39" t="n">
-        <v>1380.723936118092</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="40">
@@ -7338,16 +7338,16 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O40" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q40" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R40" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7390,7 +7390,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
         <v>125.5027119537179</v>
@@ -7402,25 +7402,25 @@
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L41" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M41" t="n">
-        <v>949.6332762537362</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N41" t="n">
-        <v>1205.91497964478</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>951.7780077424898</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872616</v>
+        <v>600.3257987549114</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>578.4347914600502</v>
       </c>
       <c r="F42" t="n">
-        <v>60.0226114399994</v>
+        <v>559.6103042500736</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463105</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>227.2652685676499</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1886.686949702618</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S42" t="n">
-        <v>1753.535205884734</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U42" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X42" t="n">
-        <v>1284.561892566739</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y42" t="n">
-        <v>1205.378667550442</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="43">
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7639,25 +7639,25 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M44" t="n">
-        <v>1009.32297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="N44" t="n">
-        <v>1651.83297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>1953.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>912.8601939406431</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C45" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000654</v>
       </c>
       <c r="D45" t="n">
-        <v>424.9805301872616</v>
+        <v>600.3257987549113</v>
       </c>
       <c r="E45" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176258</v>
       </c>
       <c r="F45" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076491</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866057</v>
+        <v>231.3278685463103</v>
       </c>
       <c r="H45" t="n">
-        <v>51.92</v>
+        <v>227.2652685676497</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>1687.299081778216</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V45" t="n">
-        <v>1268.601438150418</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W45" t="n">
-        <v>1156.103313999076</v>
+        <v>911.2836656246793</v>
       </c>
       <c r="X45" t="n">
-        <v>1056.241961023937</v>
+        <v>811.4223126495403</v>
       </c>
       <c r="Y45" t="n">
-        <v>977.0587360076396</v>
+        <v>732.239087633243</v>
       </c>
     </row>
     <row r="46">
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>239.8138871140818</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>776.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>313.7432258698271</v>
       </c>
       <c r="Q2" t="n">
-        <v>311.8831458198699</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8055,7 +8055,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N3" t="n">
-        <v>485.4085271713503</v>
+        <v>481.6508651829305</v>
       </c>
       <c r="O3" t="n">
         <v>382.6817988009037</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>705.7430074400934</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>311.8831458198699</v>
+        <v>362.3964523525329</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>879.4920535472222</v>
+        <v>410.0652014529786</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>179.1121759491998</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>879.4920535472222</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>361.7270524351312</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>879.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427137</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>721.907733095332</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>23.48346824708341</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10340,13 +10340,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L32" t="n">
-        <v>17.50927946942295</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>230.4920535472222</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>433.9659648939236</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>410.0652014529786</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>489.3624610129226</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M44" t="n">
-        <v>361.7270524351312</v>
+        <v>679.1243892794788</v>
       </c>
       <c r="N44" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.927393539209234</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23417,10 +23417,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -23654,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495950935</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23900,13 +23900,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495943084</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495907059</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25553,7 +25553,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25793,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.8382458495973992</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>797725.6530297217</v>
+        <v>797448.2902684262</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1521867.451220963</v>
+        <v>1521696.852918674</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2246009.249412206</v>
+        <v>2245838.651109917</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2969705.156810724</v>
+        <v>2969616.940008434</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3693835.387209242</v>
+        <v>3693747.170406953</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4417965.617607759</v>
+        <v>4417877.40080547</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5142095.848006274</v>
+        <v>5142007.631203984</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5866226.078404789</v>
+        <v>5866137.861602499</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6590356.308803303</v>
+        <v>6590268.092001013</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7314486.539201817</v>
+        <v>7314398.322399528</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8038616.769600337</v>
+        <v>8038528.552798048</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8762746.999998862</v>
+        <v>8762658.783196572</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9486877.230397385</v>
+        <v>9486789.013595095</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10211007.46079591</v>
+        <v>10210919.24399362</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10935137.69119443</v>
+        <v>10935049.47439214</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479587.753273076</v>
       </c>
       <c r="C2" t="n">
         <v>1479768.022390799</v>
@@ -26290,13 +26290,13 @@
         <v>1479744.38385784</v>
       </c>
       <c r="I2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479744.383857841</v>
       </c>
       <c r="J2" t="n">
         <v>1479744.38385784</v>
       </c>
       <c r="K2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479744.383857841</v>
       </c>
       <c r="L2" t="n">
         <v>1479744.383857841</v>
@@ -26308,10 +26308,10 @@
         <v>1479744.38385784</v>
       </c>
       <c r="O2" t="n">
+        <v>1479744.383857841</v>
+      </c>
+      <c r="P2" t="n">
         <v>1479744.38385784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1479744.383857841</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049332</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566727.0147207878</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457893</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308643</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>612614.6877240337</v>
+        <v>618492.2467681431</v>
       </c>
       <c r="C6" t="n">
-        <v>845721.6099115225</v>
+        <v>852065.7191412076</v>
       </c>
       <c r="D6" t="n">
-        <v>847733.2573273465</v>
+        <v>854428.807670011</v>
       </c>
       <c r="E6" t="n">
-        <v>326310.8550616651</v>
+        <v>333748.8461920195</v>
       </c>
       <c r="F6" t="n">
-        <v>917546.9178798882</v>
+        <v>924009.9090102419</v>
       </c>
       <c r="G6" t="n">
-        <v>919235.3074015408</v>
+        <v>925698.2985318954</v>
       </c>
       <c r="H6" t="n">
-        <v>920926.0403115033</v>
+        <v>927389.0314418578</v>
       </c>
       <c r="I6" t="n">
-        <v>922619.1335120507</v>
+        <v>929082.1246424062</v>
       </c>
       <c r="J6" t="n">
-        <v>535866.6041269759</v>
+        <v>542681.5952573298</v>
       </c>
       <c r="K6" t="n">
-        <v>926012.469505809</v>
+        <v>932123.4606361642</v>
       </c>
       <c r="L6" t="n">
-        <v>927712.7472281539</v>
+        <v>934175.7383585081</v>
       </c>
       <c r="M6" t="n">
-        <v>832615.4551081205</v>
+        <v>839078.4462384747</v>
       </c>
       <c r="N6" t="n">
-        <v>931120.611198885</v>
+        <v>937583.6023292392</v>
       </c>
       <c r="O6" t="n">
-        <v>676028.2337973465</v>
+        <v>682491.2249277019</v>
       </c>
       <c r="P6" t="n">
-        <v>934538.341448931</v>
+        <v>941001.3325792846</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26999,16 +26999,16 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>-0</v>
       </c>
-      <c r="L2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,13 +27100,13 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>-0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>223.3220918649904</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110.381247936798</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,19 +27557,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>31.46477465147608</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>253.5254621353083</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>294.3826718271959</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27606,22 +27606,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
-        <v>349.5087535872954</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27654,13 +27654,13 @@
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27755,22 +27755,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>92.01856822673119</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>159.5184388018133</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>88.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>30.46477465147608</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>147.2412902635512</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27837,28 +27837,28 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>283.3371250451885</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>281.3788946195025</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -27998,16 +27998,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>36.72043851444073</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>38.72409409996035</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28080,22 +28080,22 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>318.6137787494543</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>279.7728705895162</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28159,13 +28159,13 @@
         <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="H11" t="n">
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -28241,7 +28241,7 @@
         <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>191.6509141932353</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28399,10 +28399,10 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
@@ -28469,7 +28469,7 @@
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>321</v>
@@ -28478,7 +28478,7 @@
         <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="I15" t="n">
         <v>191.6509141932353</v>
@@ -28517,19 +28517,19 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28551,7 +28551,7 @@
         <v>321</v>
       </c>
       <c r="F16" t="n">
-        <v>321.0000000000021</v>
+        <v>321</v>
       </c>
       <c r="G16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28700,16 +28700,16 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28763,10 +28763,10 @@
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="Y18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28845,7 +28845,7 @@
         <v>321</v>
       </c>
       <c r="Y19" t="n">
-        <v>321.000000000003</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20">
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="C20" t="n">
         <v>321</v>
@@ -28906,7 +28906,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29152,7 +29152,7 @@
         <v>321</v>
       </c>
       <c r="V23" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="W23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29319,7 +29319,7 @@
         <v>321</v>
       </c>
       <c r="Y25" t="n">
-        <v>321.0000000000067</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470187</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,19 +29408,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
@@ -29456,7 +29456,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
@@ -29468,7 +29468,7 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29651,13 +29651,13 @@
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29705,7 +29705,7 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>226.036732227374</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
     </row>
     <row r="31">
@@ -29815,7 +29815,7 @@
         <v>321</v>
       </c>
       <c r="F32" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="G32" t="n">
         <v>321</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29885,16 +29885,16 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29927,13 +29927,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
@@ -29942,10 +29942,10 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30122,10 +30122,10 @@
         <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -30185,7 +30185,7 @@
         <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30356,22 +30356,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="G39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>321</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>321</v>
@@ -30410,7 +30410,7 @@
         <v>321</v>
       </c>
       <c r="T39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>321</v>
@@ -30596,7 +30596,7 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -30605,16 +30605,16 @@
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126195</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30659,7 +30659,7 @@
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30833,16 +30833,16 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30851,7 +30851,7 @@
         <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126212</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30887,7 +30887,7 @@
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>292.4851886216195</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>373</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.3412755627363</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>188.4896145353295</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8.846453771640441</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34898,16 +34898,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>178.4067078032426</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,25 +34980,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>300.210210236103</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
+        <v>234.1880104510425</v>
+      </c>
+      <c r="N5" t="n">
         <v>374</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
         <v>374</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35123,10 +35123,10 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>2.35622020823202</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>6.996038651760555</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -35138,7 +35138,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35171,7 +35171,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35220,13 +35220,13 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824119</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>374</v>
@@ -35235,10 +35235,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.3412755627363</v>
+        <v>234.28870772354</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35366,16 +35366,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>73.75384033415376</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>52.65312153707789</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
+        <v>648.9999999999999</v>
+      </c>
+      <c r="L11" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M11" t="n">
         <v>649</v>
       </c>
-      <c r="L11" t="n">
-        <v>649</v>
-      </c>
-      <c r="M11" t="n">
-        <v>179.1121759491996</v>
-      </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>261.4423154327527</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L14" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M14" t="n">
+        <v>60.29262328527617</v>
+      </c>
+      <c r="N14" t="n">
         <v>649</v>
-      </c>
-      <c r="L14" t="n">
-        <v>649</v>
-      </c>
-      <c r="M14" t="n">
-        <v>649</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35837,13 +35837,13 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>46.61714403226019</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G16" t="n">
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35931,16 +35931,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36131,7 +36131,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y19" t="n">
-        <v>33.53464715054066</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="20">
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>60.29262328527617</v>
+        <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>609.8778844919133</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L23" t="n">
         <v>218.2342914572864</v>
@@ -36414,7 +36414,7 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36605,7 +36605,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y25" t="n">
-        <v>33.5346471505443</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="26">
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L26" t="n">
-        <v>649.0000000000001</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>420.473303945477</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36879,16 +36879,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L29" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37119,13 +37119,13 @@
         <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7435709267094</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
         <v>175.9119195979899</v>
@@ -37368,10 +37368,10 @@
         <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
-        <v>198.5777841804241</v>
+        <v>632.5437490743477</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>258.8704074657004</v>
+        <v>649</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M44" t="n">
-        <v>60.29262328527617</v>
+        <v>377.6899601296238</v>
       </c>
       <c r="N44" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
